--- a/data/trans_camb/IP1004-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 0,0</t>
+          <t>-6,51; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 0,0</t>
+          <t>-6,49; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 6,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,44</t>
+          <t>-1,22; 2,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,0</t>
+          <t>-3,41; 0,0</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,0</t>
+          <t>-3,37; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,0</t>
+          <t>-3,37; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,0</t>
+          <t>-1,59; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,0</t>
+          <t>-1,59; 0,0</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,22</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,0</t>
+          <t>-5,72; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 0,0</t>
+          <t>-5,45; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,0</t>
+          <t>-3,2; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,7</t>
+          <t>-2,46; 0,7</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,81</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 0,0</t>
+          <t>-7,82; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 0,0</t>
+          <t>-7,05; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,0</t>
+          <t>-3,68; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,6</t>
+          <t>-1,64; 2,62</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 0,0</t>
+          <t>-7,05; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 0,0</t>
+          <t>-7,05; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,0</t>
+          <t>-6,58; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 0,0</t>
+          <t>-5,83; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,0</t>
+          <t>-4,07; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,0</t>
+          <t>-3,63; 0,0</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,33</t>
+          <t>-0,51; 0,23</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,38</t>
+          <t>-0,42; 0,39</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,36</t>
+          <t>-0,62; 0,46</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; -0,17</t>
+          <t>-1,02; -0,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,24</t>
+          <t>-0,46; 0,19</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,0</t>
+          <t>-0,61; -0,0</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 368,78</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-87,83; 178,42</t>
+          <t>-87,33; 175,47</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,45</t>
+          <t>-100,0; 73,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Provincia-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 0,0</t>
+          <t>-6,49; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,0</t>
+          <t>-6,45; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,91</t>
+          <t>0,0; 9,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,32</t>
+          <t>-1,22; 2,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,0</t>
+          <t>-2,66; 0,0</t>
         </is>
       </c>
     </row>
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,0</t>
+          <t>-3,07; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,0</t>
+          <t>-3,07; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,0</t>
+          <t>-1,79; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,0</t>
+          <t>-1,79; 0,0</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 6,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 0,0</t>
+          <t>-5,64; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 0,0</t>
+          <t>-5,86; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,0</t>
+          <t>-2,56; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,7</t>
+          <t>-2,11; 0,7</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,99</t>
+          <t>0,0; 9,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 0,0</t>
+          <t>-7,93; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,0</t>
+          <t>-7,86; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,0</t>
+          <t>-4,67; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,62</t>
+          <t>-2,41; 2,65</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,0</t>
+          <t>-6,55; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,0</t>
+          <t>-6,55; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 0,0</t>
+          <t>-4,51; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 0,0</t>
+          <t>-5,21; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,0</t>
+          <t>-3,91; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,0</t>
+          <t>-3,9; 0,0</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,23</t>
+          <t>-0,52; 0,23</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,39</t>
+          <t>-0,42; 0,37</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,46</t>
+          <t>-0,64; 0,41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,02; -0,17</t>
+          <t>-1,0; -0,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,19</t>
+          <t>-0,42; 0,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,61; -0,0</t>
+          <t>-0,57; -0,0</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 368,78</t>
+          <t>-100,0; 352,0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 175,47</t>
+          <t>-85,69; 230,9</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,73</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-1,3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,0</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,7</t>
+          <t>-7,51; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,42; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,34</t>
+          <t>-1,22; 2,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,0</t>
+          <t>-3,63; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,61</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,72; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,72; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,0</t>
+          <t>-1,81; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,0</t>
+          <t>-1,81; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,77</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,38; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>-5,08; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,0</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,0</t>
+          <t>-2,88; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,7</t>
+          <t>-2,12; 0,7</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,57</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,57</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,78</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,87; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,45</t>
+          <t>-6,33; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 0,0</t>
+          <t>0,0; 8,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,0</t>
+          <t>-4,08; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,65</t>
+          <t>-1,65; 2,6</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-1,31</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-1,31</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 0,0</t>
+          <t>-5,32; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 0,0</t>
+          <t>-6,18; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,0</t>
+          <t>-6,52; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 0,0</t>
+          <t>-6,52; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,0</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,0</t>
+          <t>-3,74; 0,0</t>
         </is>
       </c>
     </row>
@@ -1685,17 +1685,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0,45</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>0,48</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-0,01</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,23</t>
+          <t>-0,67; 0,36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,37</t>
+          <t>-1,0; -0,17</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,41</t>
+          <t>-0,42; 0,33</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; -0,17</t>
+          <t>-0,42; 0,38</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,24</t>
+          <t>-0,43; 0,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; -0,0</t>
+          <t>-0,54; 0,0</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-29,4%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-46,2%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-7,07%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-29,4%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-85,69; 230,9</t>
+          <t>-87,83; 178,42</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 68,45</t>
         </is>
       </c>
     </row>
